--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLIII/LTAIPT_A63F43A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="133">
   <si>
     <t>49014</t>
   </si>
@@ -142,7 +142,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Ingresos por Venta de Bienes, Prestación de Servicios y Otros Ingresos</t>
@@ -163,263 +163,256 @@
     <t/>
   </si>
   <si>
+    <t>Productos</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Aprovechamientos</t>
+  </si>
+  <si>
     <t>Transferencias, Asignaciones, Subsidios y Otras Ayudas</t>
   </si>
   <si>
     <t>Subsidios y Subvenciones</t>
   </si>
   <si>
+    <t>Recursos Estatales</t>
+  </si>
+  <si>
+    <t>58517</t>
+  </si>
+  <si>
     <t>Recursos Federales</t>
   </si>
   <si>
     <t>Subsecretaría de Educación Media Superior</t>
   </si>
   <si>
-    <t>Productos</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Derechos</t>
-  </si>
-  <si>
-    <t>Derechos por Prestación de Servicios</t>
-  </si>
-  <si>
-    <t>Participaciones, Aportaciones, Convenios, Incentivos Derivados de la Colaboración Fiscal y
-Fondos Distintos de Aportaciones</t>
-  </si>
-  <si>
-    <t>Aportaciones</t>
-  </si>
-  <si>
-    <t>105662</t>
-  </si>
-  <si>
-    <t>Transferencias Federales Etiquetadas</t>
-  </si>
-  <si>
-    <t>166667</t>
-  </si>
-  <si>
-    <t>Recursos Estatales</t>
-  </si>
-  <si>
-    <t>130135</t>
-  </si>
-  <si>
-    <t>25568853</t>
-  </si>
-  <si>
-    <t>AC6D195875F212BD7B1E07908890419B</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>42228.7</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Depto.%20de%20Programacion%20y%20Presupuesto/2do_Trimestre/Informacion%20Preupuestal/Informacion%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>15/07/2022</t>
-  </si>
-  <si>
-    <t>D3AC5C28EA709FB43CA7060183113FFA</t>
-  </si>
-  <si>
-    <t>413434.91</t>
-  </si>
-  <si>
-    <t>A83391BBEBBC1D960E0AFD8B26976368</t>
-  </si>
-  <si>
-    <t>98639</t>
-  </si>
-  <si>
-    <t>13/06/2022</t>
-  </si>
-  <si>
-    <t>B4D6CC40677013AA02E9A7DEC71A4D32</t>
-  </si>
-  <si>
-    <t>45CB16156B0A85FF9C214E800DABFBBA</t>
-  </si>
-  <si>
-    <t>15EF69BF9B805B0879DAB9CD05FDE582</t>
-  </si>
-  <si>
-    <t>117290.75</t>
-  </si>
-  <si>
-    <t>9C1DFD474FD45B62C3B40EF9A4A8061D</t>
-  </si>
-  <si>
-    <t>11708561.5</t>
-  </si>
-  <si>
-    <t>20/06/2022</t>
-  </si>
-  <si>
-    <t>819D54D625DF38E70013FB27797D0A45</t>
-  </si>
-  <si>
-    <t>4C4279FF16546A7B491F6B6A88B33386</t>
-  </si>
-  <si>
-    <t>16/06/2022</t>
-  </si>
-  <si>
-    <t>73DC196501C0C4788F0309B01C057AF7</t>
-  </si>
-  <si>
-    <t>16858584</t>
-  </si>
-  <si>
-    <t>17/06/2022</t>
-  </si>
-  <si>
-    <t>27DB40E6938086958B5DB0AA72D440CC</t>
-  </si>
-  <si>
-    <t>29214.21</t>
-  </si>
-  <si>
-    <t>31/05/2022</t>
-  </si>
-  <si>
-    <t>0D5CE56CADFFAB5064BF97DFEDBEBBB8</t>
-  </si>
-  <si>
-    <t>332905.83</t>
-  </si>
-  <si>
-    <t>7D6F1CA6C7193302F5CE16E9DCE1996F</t>
-  </si>
-  <si>
-    <t>551828</t>
-  </si>
-  <si>
-    <t>12/05/2022</t>
-  </si>
-  <si>
-    <t>F565FAB809C09B2D07905D274F43476A</t>
-  </si>
-  <si>
-    <t>009102354D443D808E380E05E1F38CC5</t>
-  </si>
-  <si>
-    <t>CFBE8C4335B04918FC31ACF8F4869925</t>
-  </si>
-  <si>
-    <t>115017.75</t>
-  </si>
-  <si>
-    <t>0892287C4B2F71FCCD0521A963DCB848</t>
-  </si>
-  <si>
-    <t>7488828.99</t>
-  </si>
-  <si>
-    <t>19/05/2022</t>
-  </si>
-  <si>
-    <t>9460992D22831B96E4942EF4628ED5C5</t>
-  </si>
-  <si>
-    <t>610B4D3A0FA3D15D2D6446FC2B3B56BE</t>
-  </si>
-  <si>
-    <t>10754040.5</t>
-  </si>
-  <si>
-    <t>719BBAF5627A348D4F456A6D5B78FEB6</t>
-  </si>
-  <si>
-    <t>F7B0B3000601049BF62390100821E2FE</t>
-  </si>
-  <si>
-    <t>16/05/2022</t>
-  </si>
-  <si>
-    <t>6FE2003724047004ECDC43E03DF0C25D</t>
-  </si>
-  <si>
-    <t>D6EB8A35F719D8CB20DBBA90512F1687</t>
-  </si>
-  <si>
-    <t>32262.33</t>
-  </si>
-  <si>
-    <t>30/04/2022</t>
-  </si>
-  <si>
-    <t>951BE1A7A0B4150FF4884CC4D7930113</t>
-  </si>
-  <si>
-    <t>274550.34</t>
-  </si>
-  <si>
-    <t>E38E8F88CAA5801032AFF42655497F5D</t>
-  </si>
-  <si>
-    <t>593844</t>
-  </si>
-  <si>
-    <t>18/04/2022</t>
-  </si>
-  <si>
-    <t>128B6DDC683D8EE54C578C6F6C3654F7</t>
-  </si>
-  <si>
-    <t>29/04/2022</t>
-  </si>
-  <si>
-    <t>8375FCA2F3E182115AFB33DB8C7B37AF</t>
-  </si>
-  <si>
-    <t>5CB6BC343810133ACC4049FF25C964B7</t>
-  </si>
-  <si>
-    <t>149367.75</t>
-  </si>
-  <si>
-    <t>EF1A13CB69C177B9F645CD4327B57908</t>
-  </si>
-  <si>
-    <t>3015696.95</t>
-  </si>
-  <si>
-    <t>25/04/2022</t>
-  </si>
-  <si>
-    <t>78048F47D4D6884FCE40A15A5973FF28</t>
-  </si>
-  <si>
-    <t>11437162.5</t>
-  </si>
-  <si>
-    <t>CE0B84AE7B1511E20A2F4F7495FB1DEC</t>
-  </si>
-  <si>
-    <t>F4F3C20151087E2189045C5311C4B004</t>
-  </si>
-  <si>
-    <t>24C11A8F25020EF73B4B72F9CF4B64A8</t>
-  </si>
-  <si>
-    <t>12/04/2022</t>
-  </si>
-  <si>
-    <t>78EAE179D3A7AB35711EDCDF79BBE0F3</t>
-  </si>
-  <si>
-    <t>11/04/2022</t>
+    <t>135980</t>
+  </si>
+  <si>
+    <t>6E22AB6512E1274F0D421E5AD7763F06</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>26674055</t>
+  </si>
+  <si>
+    <t>14/04/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Presupuestal/Informaci%c3%b3n%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>21/07/2023</t>
+  </si>
+  <si>
+    <t>3050D3BC20CD4065C2253C14A7A4B86F</t>
+  </si>
+  <si>
+    <t>13/04/2023</t>
+  </si>
+  <si>
+    <t>D391B7845DD41FEE10807B342E0C5334</t>
+  </si>
+  <si>
+    <t>7476007.7</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t>B91BC8FC1597CA8C3B100EA1E1AC7261</t>
+  </si>
+  <si>
+    <t>400095.25</t>
+  </si>
+  <si>
+    <t>C6E9E64A0CB54EC4F6882DA4746F4D44</t>
+  </si>
+  <si>
+    <t>8115154.2</t>
+  </si>
+  <si>
+    <t>27/04/2023</t>
+  </si>
+  <si>
+    <t>148CC71CA0CF9A3F91E033C800020FE6</t>
+  </si>
+  <si>
+    <t>1039241.75</t>
+  </si>
+  <si>
+    <t>462D1B54C5D98D5BE637EEEDE6075ACF</t>
+  </si>
+  <si>
+    <t>74721</t>
+  </si>
+  <si>
+    <t>6F5EB8FFEE44B0046B8C1DE8B8381051</t>
+  </si>
+  <si>
+    <t>78583</t>
+  </si>
+  <si>
+    <t>9AEAC561048D44E365154B248D389CB1</t>
+  </si>
+  <si>
+    <t>609484</t>
+  </si>
+  <si>
+    <t>28/04/2023</t>
+  </si>
+  <si>
+    <t>CF62BDF4894F331953220151437F72A3</t>
+  </si>
+  <si>
+    <t>27622.12</t>
+  </si>
+  <si>
+    <t>30/04/2023</t>
+  </si>
+  <si>
+    <t>9004E5958DB7D3009BD7FCFCEF378206</t>
+  </si>
+  <si>
+    <t>295511</t>
+  </si>
+  <si>
+    <t>856A6426706C92261DC8A4C63EE5EE29</t>
+  </si>
+  <si>
+    <t>17587289</t>
+  </si>
+  <si>
+    <t>10/05/2023</t>
+  </si>
+  <si>
+    <t>0453C254E40D81096103FE6691DFE52B</t>
+  </si>
+  <si>
+    <t>E0389A486ED06A2BE89EB2F8B7167DFC</t>
+  </si>
+  <si>
+    <t>8503629</t>
+  </si>
+  <si>
+    <t>17/05/2023</t>
+  </si>
+  <si>
+    <t>035F8AE7BBFE02B2E1B94C0B3B87C807</t>
+  </si>
+  <si>
+    <t>666250</t>
+  </si>
+  <si>
+    <t>457E333D05B25D8DD0A3CB03772B0A78</t>
+  </si>
+  <si>
+    <t>9110466</t>
+  </si>
+  <si>
+    <t>26/05/2023</t>
+  </si>
+  <si>
+    <t>9B8DB1E9A275EA01F4F36C77F536A144</t>
+  </si>
+  <si>
+    <t>1273087</t>
+  </si>
+  <si>
+    <t>6F65AC87A2C07802FE588445518C6956</t>
+  </si>
+  <si>
+    <t>29/05/2023</t>
+  </si>
+  <si>
+    <t>4877DF93D27D338C128F5B050335BEBC</t>
+  </si>
+  <si>
+    <t>60437</t>
+  </si>
+  <si>
+    <t>30/05/2023</t>
+  </si>
+  <si>
+    <t>FFF0AD9E328FD23C70ABF19C6A2B42B4</t>
+  </si>
+  <si>
+    <t>158449</t>
+  </si>
+  <si>
+    <t>ABF857B02901CB29C381D5362D610EA6</t>
+  </si>
+  <si>
+    <t>17711.69</t>
+  </si>
+  <si>
+    <t>31/05/2023</t>
+  </si>
+  <si>
+    <t>0259CBEA639934CAAFB3CA3B9A95689E</t>
+  </si>
+  <si>
+    <t>421200.84</t>
+  </si>
+  <si>
+    <t>C6F8C008F66CF6C2387C56250761305A</t>
+  </si>
+  <si>
+    <t>26/06/2023</t>
+  </si>
+  <si>
+    <t>B8DDA4602C453437C6F06D5E024CA2D9</t>
+  </si>
+  <si>
+    <t>09/06/2023</t>
+  </si>
+  <si>
+    <t>9A94A392A020B806D8469CF122A56AEA</t>
+  </si>
+  <si>
+    <t>13118102</t>
+  </si>
+  <si>
+    <t>C43892A16815E4910310D5184EABB3CB</t>
+  </si>
+  <si>
+    <t>11678730</t>
+  </si>
+  <si>
+    <t>B30C877491E63196AF3A37E140B6E69A</t>
+  </si>
+  <si>
+    <t>121227</t>
+  </si>
+  <si>
+    <t>231BDB2972B24264D3B6FC4A25747E91</t>
+  </si>
+  <si>
+    <t>131139</t>
+  </si>
+  <si>
+    <t>28/06/2023</t>
+  </si>
+  <si>
+    <t>AF7340A9ED11CCE7E2AB32D2D8F69C3A</t>
+  </si>
+  <si>
+    <t>16120.13</t>
+  </si>
+  <si>
+    <t>E913E39A1D81309E2888CD001443C570</t>
+  </si>
+  <si>
+    <t>263898.3</t>
   </si>
 </sst>
 </file>
@@ -812,20 +805,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="185.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -1022,46 +1015,46 @@
     </row>
     <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>48</v>
@@ -1069,46 +1062,46 @@
     </row>
     <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>48</v>
@@ -1116,46 +1109,46 @@
     </row>
     <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>48</v>
@@ -1163,46 +1156,46 @@
     </row>
     <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>48</v>
@@ -1210,46 +1203,46 @@
     </row>
     <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>48</v>
@@ -1257,28 +1250,28 @@
     </row>
     <row r="13" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>46</v>
@@ -1287,16 +1280,16 @@
         <v>75</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>48</v>
@@ -1304,46 +1297,46 @@
     </row>
     <row r="14" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>48</v>
@@ -1351,28 +1344,28 @@
     </row>
     <row r="15" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>81</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>46</v>
@@ -1381,16 +1374,16 @@
         <v>75</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>48</v>
@@ -1398,46 +1391,46 @@
     </row>
     <row r="16" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>48</v>
@@ -1445,46 +1438,46 @@
     </row>
     <row r="17" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>48</v>
@@ -1492,46 +1485,46 @@
     </row>
     <row r="18" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>48</v>
@@ -1539,46 +1532,46 @@
     </row>
     <row r="19" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="K19" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>48</v>
@@ -1586,46 +1579,46 @@
     </row>
     <row r="20" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>48</v>
@@ -1633,46 +1626,46 @@
     </row>
     <row r="21" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>48</v>
@@ -1680,46 +1673,46 @@
     </row>
     <row r="22" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>48</v>
@@ -1733,40 +1726,40 @@
         <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>48</v>
@@ -1774,46 +1767,46 @@
     </row>
     <row r="24" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>48</v>
@@ -1827,40 +1820,40 @@
         <v>42</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>48</v>
@@ -1868,46 +1861,46 @@
     </row>
     <row r="26" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>48</v>
@@ -1915,28 +1908,28 @@
     </row>
     <row r="27" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>46</v>
@@ -1945,16 +1938,16 @@
         <v>96</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>48</v>
@@ -1962,46 +1955,46 @@
     </row>
     <row r="28" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>48</v>
@@ -2009,46 +2002,46 @@
     </row>
     <row r="29" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>48</v>
@@ -2056,46 +2049,46 @@
     </row>
     <row r="30" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>48</v>
@@ -2103,46 +2096,46 @@
     </row>
     <row r="31" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="I31" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>48</v>
@@ -2150,46 +2143,46 @@
     </row>
     <row r="32" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>48</v>
@@ -2197,46 +2190,46 @@
     </row>
     <row r="33" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>48</v>
@@ -2244,46 +2237,46 @@
     </row>
     <row r="34" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>48</v>
@@ -2291,46 +2284,46 @@
     </row>
     <row r="35" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>48</v>
@@ -2338,46 +2331,46 @@
     </row>
     <row r="36" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J36" s="2" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>48</v>
@@ -2385,236 +2378,48 @@
     </row>
     <row r="37" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="J37" s="2" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O41" s="2" t="s">
         <v>48</v>
       </c>
     </row>
